--- a/01_数据/杜邦分析_数据录入及分析.xlsx
+++ b/01_数据/杜邦分析_数据录入及分析.xlsx
@@ -16,7 +16,7 @@
     <sheet name="利润表" sheetId="2" r:id="rId2"/>
     <sheet name="资产负债表" sheetId="3" r:id="rId3"/>
     <sheet name="杜邦速算" sheetId="4" r:id="rId4"/>
-    <sheet name="研究_经营性占款+高分红" sheetId="5" r:id="rId5"/>
+    <sheet name="分析研究_经营性占款+高分红" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">利润表!$A$1:$R$15</definedName>
@@ -1748,6 +1748,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
@@ -1756,14 +1762,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Arial"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1773,8 +1772,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
   </fonts>

--- a/01_数据/杜邦分析_数据录入及分析.xlsx
+++ b/01_数据/杜邦分析_数据录入及分析.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\桃花林\Desktop\2026求职\杜邦分析项目\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\桃花林\Desktop\2026求职\作品集\杜邦分析项目\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8055" tabRatio="500" activeTab="4"/>
+    <workbookView windowWidth="19200" windowHeight="8055" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使用说明" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,8 @@
     <sheet name="分析研究_经营性占款+高分红" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">利润表!$A$1:$R$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">资产负债表!$A$1:$T$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">利润表!$A$1:$S$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">资产负债表!$A$1:$AB$19</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="97">
   <si>
     <r>
       <rPr>
@@ -681,6 +681,9 @@
     <t>少数股东损益</t>
   </si>
   <si>
+    <t>现金分红</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -983,6 +986,30 @@
     <t>所有者权益合计</t>
   </si>
   <si>
+    <t>应付票据</t>
+  </si>
+  <si>
+    <t>应付账款</t>
+  </si>
+  <si>
+    <t>合同负债</t>
+  </si>
+  <si>
+    <t>应付职工薪酬</t>
+  </si>
+  <si>
+    <t>应交税费</t>
+  </si>
+  <si>
+    <t>短期借款</t>
+  </si>
+  <si>
+    <t>一年内到期非流动负债</t>
+  </si>
+  <si>
+    <t>租赁负债</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1458,40 +1485,16 @@
     <t>总负债</t>
   </si>
   <si>
-    <t>应付票据</t>
-  </si>
-  <si>
-    <t>应付账款</t>
-  </si>
-  <si>
-    <t>合同负债</t>
-  </si>
-  <si>
-    <t>应付职工薪酬</t>
-  </si>
-  <si>
-    <t>应交税费</t>
-  </si>
-  <si>
     <t>经营性负债</t>
   </si>
   <si>
     <t>经营性负债占比</t>
   </si>
   <si>
-    <t>短期借款</t>
-  </si>
-  <si>
     <t>长期借款</t>
   </si>
   <si>
     <t>应付债券</t>
-  </si>
-  <si>
-    <t>一年内到期非流动负债</t>
-  </si>
-  <si>
-    <t>租赁负债</t>
   </si>
   <si>
     <t>有息负债合计</t>
@@ -1515,7 +1518,7 @@
     <numFmt numFmtId="176" formatCode="#,##0.00;\(#,##0.00\);\-"/>
     <numFmt numFmtId="177" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="39">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1583,6 +1586,13 @@
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Noto Sans CJK SC"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1767,13 +1777,13 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="12"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -2120,31 +2130,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2153,119 +2160,122 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2299,10 +2309,13 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2621,50 +2634,50 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1" spans="2:2">
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="24" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1" spans="2:2">
-      <c r="B2" s="24"/>
+      <c r="B2" s="25"/>
     </row>
     <row r="3" ht="30" customHeight="1" spans="2:2">
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="25" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="2:2">
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="25" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="2:2">
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="25" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="2:2">
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="25" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="2:2">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="25" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="2:2">
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="25" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="2:2">
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="25" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="2:2">
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="25" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2678,7 +2691,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr defaultColWidth="8.66371681415929" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -2691,11 +2704,12 @@
     <col min="13" max="13" width="14" customWidth="1"/>
     <col min="14" max="15" width="15.5309734513274" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
-    <col min="18" max="18" width="34" customWidth="1"/>
+    <col min="17" max="17" width="16.3185840707965" customWidth="1"/>
+    <col min="18" max="18" width="18" customWidth="1"/>
+    <col min="19" max="19" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26.25" spans="1:18">
+    <row r="1" ht="26.25" spans="1:19">
       <c r="A1" s="9" t="s">
         <v>9</v>
       </c>
@@ -2744,19 +2758,22 @@
       <c r="P1" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="23" t="s">
         <v>25</v>
       </c>
       <c r="R1" s="9" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:18">
+      <c r="S1" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="20">
         <v>2021</v>
@@ -2813,20 +2830,24 @@
         <f>-2572081.05</f>
         <v>-2572081.05</v>
       </c>
-      <c r="Q2" s="21">
-        <f t="shared" ref="Q2:Q15" si="0">IF(COUNT(N2:P2)&lt;3,"",N2-O2-P2)</f>
+      <c r="Q2" s="4">
+        <f>'分析研究_经营性占款+高分红'!F2</f>
+        <v>1560749458.68</v>
+      </c>
+      <c r="R2" s="21">
+        <f t="shared" ref="R2:R15" si="0">IF(COUNT(N2:P2)&lt;3,"",N2-O2-P2)</f>
         <v>4.74974513053894e-8</v>
       </c>
-      <c r="R2" s="18" t="s">
+      <c r="S2" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="19" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
-      <c r="A3" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>28</v>
       </c>
       <c r="C3" s="20">
         <v>2022</v>
@@ -2883,20 +2904,24 @@
         <f>-1483087.35</f>
         <v>-1483087.35</v>
       </c>
-      <c r="Q3" s="21">
+      <c r="Q3" s="4">
+        <f>'分析研究_经营性占款+高分红'!E2</f>
+        <v>2439504228.21</v>
+      </c>
+      <c r="R3" s="21">
         <f t="shared" si="0"/>
         <v>-1.42958015203476e-7</v>
       </c>
-      <c r="R3" s="18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
+      <c r="S3" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
       <c r="A4" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="20">
         <v>2023</v>
@@ -2953,20 +2978,24 @@
         <f>-377710.06</f>
         <v>-377710.06</v>
       </c>
-      <c r="Q4" s="21">
+      <c r="Q4" s="4">
+        <f>'分析研究_经营性占款+高分红'!D2</f>
+        <v>2175512858.61</v>
+      </c>
+      <c r="R4" s="21">
         <f t="shared" si="0"/>
         <v>5.72181306779385e-8</v>
       </c>
-      <c r="R4" s="18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
+      <c r="S4" s="18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="A5" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" s="20">
         <v>2024</v>
@@ -3023,20 +3052,24 @@
         <f>799451.45</f>
         <v>799451.45</v>
       </c>
-      <c r="Q5" s="21">
+      <c r="Q5" s="4">
+        <f>'分析研究_经营性占款+高分红'!C2</f>
+        <v>2238705174.73</v>
+      </c>
+      <c r="R5" s="21">
         <f t="shared" si="0"/>
         <v>2.86148861050606e-7</v>
       </c>
-      <c r="R5" s="18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
+      <c r="S5" s="18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="20">
         <v>2025</v>
@@ -3093,20 +3126,24 @@
         <f>-2407202.22</f>
         <v>-2407202.22</v>
       </c>
-      <c r="Q6" s="21">
+      <c r="Q6" s="4">
+        <f>'分析研究_经营性占款+高分红'!B2</f>
+        <v>2095710650.28</v>
+      </c>
+      <c r="R6" s="21">
         <f t="shared" si="0"/>
         <v>-2.84053385257721e-8</v>
       </c>
-      <c r="R6" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
+      <c r="S6" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7" s="18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" s="20">
         <v>2023</v>
@@ -3163,20 +3200,21 @@
         <f>1502672.88</f>
         <v>1502672.88</v>
       </c>
-      <c r="Q7" s="21">
+      <c r="Q7" s="4"/>
+      <c r="R7" s="21">
         <f t="shared" si="0"/>
         <v>-4.65661287307739e-9</v>
       </c>
-      <c r="R7" s="18" t="s">
+      <c r="S7" s="18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="A8" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="19" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="A8" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>35</v>
       </c>
       <c r="C8" s="20">
         <v>2024</v>
@@ -3233,20 +3271,21 @@
         <f>-15922221.04</f>
         <v>-15922221.04</v>
       </c>
-      <c r="Q8" s="21">
+      <c r="Q8" s="4"/>
+      <c r="R8" s="21">
         <f t="shared" si="0"/>
         <v>7.45058059692383e-9</v>
       </c>
-      <c r="R8" s="18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
+      <c r="S8" s="18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9" s="18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" s="20">
         <v>2025</v>
@@ -3303,20 +3342,21 @@
         <f>-510752.62</f>
         <v>-510752.62</v>
       </c>
-      <c r="Q9" s="21">
+      <c r="Q9" s="4"/>
+      <c r="R9" s="21">
         <f t="shared" si="0"/>
         <v>-4.77302819490433e-9</v>
       </c>
-      <c r="R9" s="18" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
+      <c r="S9" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
       <c r="A10" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" s="20">
         <v>2023</v>
@@ -3373,20 +3413,21 @@
         <f>31933.92</f>
         <v>31933.92</v>
       </c>
-      <c r="Q10" s="21">
+      <c r="Q10" s="4"/>
+      <c r="R10" s="21">
         <f t="shared" si="0"/>
         <v>1.66910467669368e-8</v>
       </c>
-      <c r="R10" s="18" t="s">
+      <c r="S10" s="18" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
+      <c r="A11" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="19" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>40</v>
       </c>
       <c r="C11" s="20">
         <v>2024</v>
@@ -3443,20 +3484,21 @@
         <f>18320533.03</f>
         <v>18320533.03</v>
       </c>
-      <c r="Q11" s="21">
+      <c r="Q11" s="4"/>
+      <c r="R11" s="21">
         <f t="shared" si="0"/>
         <v>-2.98023223876953e-8</v>
       </c>
-      <c r="R11" s="18" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
+      <c r="S11" s="18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
       <c r="A12" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" s="20">
         <v>2025</v>
@@ -3513,20 +3555,21 @@
         <f>27045639.88</f>
         <v>27045639.88</v>
       </c>
-      <c r="Q12" s="21">
+      <c r="Q12" s="4"/>
+      <c r="R12" s="21">
         <f t="shared" si="0"/>
         <v>-3.72529029846191e-9</v>
       </c>
-      <c r="R12" s="18" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
+      <c r="S12" s="18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
       <c r="A13" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C13" s="20">
         <v>2023</v>
@@ -3583,20 +3626,21 @@
         <f>69475248.27</f>
         <v>69475248.27</v>
       </c>
-      <c r="Q13" s="21">
+      <c r="Q13" s="4"/>
+      <c r="R13" s="21">
         <f t="shared" si="0"/>
         <v>-1.49011611938477e-8</v>
       </c>
-      <c r="R13" s="18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
+      <c r="S13" s="18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
       <c r="A14" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C14" s="20">
         <v>2024</v>
@@ -3653,20 +3697,21 @@
         <f>62645194.15</f>
         <v>62645194.15</v>
       </c>
-      <c r="Q14" s="21">
+      <c r="Q14" s="4"/>
+      <c r="R14" s="21">
         <f t="shared" si="0"/>
         <v>-2.23517417907715e-8</v>
       </c>
-      <c r="R14" s="18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
+      <c r="S14" s="18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
       <c r="A15" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C15" s="20">
         <v>2025</v>
@@ -3723,16 +3768,17 @@
         <f>44983858.96</f>
         <v>44983858.96</v>
       </c>
-      <c r="Q15" s="21">
+      <c r="Q15" s="4"/>
+      <c r="R15" s="21">
         <f t="shared" si="0"/>
         <v>3.72529029846191e-8</v>
       </c>
-      <c r="R15" s="18" t="s">
-        <v>33</v>
+      <c r="S15" s="18" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:R15" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:S15" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3744,7 +3790,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:AB19"/>
   <sheetFormatPr defaultColWidth="8.66371681415929" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -3757,12 +3803,12 @@
     <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="13" width="15.5309734513274" customWidth="1"/>
     <col min="14" max="14" width="14" customWidth="1"/>
-    <col min="15" max="15" width="15.5309734513274" customWidth="1"/>
-    <col min="16" max="19" width="18" customWidth="1"/>
-    <col min="20" max="20" width="34" customWidth="1"/>
+    <col min="15" max="23" width="15.5309734513274" customWidth="1"/>
+    <col min="24" max="27" width="18" customWidth="1"/>
+    <col min="28" max="28" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="29.25" spans="1:20">
+    <row r="1" ht="29.25" spans="1:28">
       <c r="A1" s="9" t="s">
         <v>9</v>
       </c>
@@ -3770,66 +3816,90 @@
         <v>10</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S1" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T1" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20">
+        <v>64</v>
+      </c>
+      <c r="U1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="V1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="W1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="X1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB1" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28">
       <c r="A2" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="20">
         <v>2020</v>
@@ -3870,32 +3940,40 @@
       <c r="O2" s="4">
         <v>7236723990.03</v>
       </c>
-      <c r="P2" s="21">
-        <f t="shared" ref="P2:P19" si="0">IF(COUNT(I2,L2,O2)&lt;3,"",I2-L2-O2)</f>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="21">
+        <f t="shared" ref="X2:X19" si="0">IF(COUNT(I2,L2,O2)&lt;3,"",I2-L2-O2)</f>
         <v>-9.5367431640625e-7</v>
       </c>
-      <c r="Q2" s="21">
-        <f t="shared" ref="Q2:Q19" si="1">IF(COUNT(M2:O2)&lt;3,"",O2-M2-N2)</f>
+      <c r="Y2" s="21">
+        <f t="shared" ref="Y2:Y19" si="1">IF(COUNT(M2:O2)&lt;3,"",O2-M2-N2)</f>
         <v>-3.42726707458496e-7</v>
       </c>
-      <c r="R2" s="21" t="b">
+      <c r="Z2" s="21" t="b">
         <f>L2=K2+J2</f>
         <v>1</v>
       </c>
-      <c r="S2" s="21" t="b">
+      <c r="AA2" s="21" t="b">
         <f>I2=G2+H2</f>
         <v>1</v>
       </c>
-      <c r="T2" s="18" t="s">
+      <c r="AB2" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28">
+      <c r="A3" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="19" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20">
-      <c r="A3" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>28</v>
       </c>
       <c r="C3" s="20">
         <v>2021</v>
@@ -3936,32 +4014,64 @@
       <c r="O3" s="4">
         <v>7658307846.92</v>
       </c>
-      <c r="P3" s="21">
+      <c r="P3" s="4">
+        <f>'分析研究_经营性占款+高分红'!F6</f>
+        <v>500250000</v>
+      </c>
+      <c r="Q3" s="4">
+        <f>'分析研究_经营性占款+高分红'!F7</f>
+        <v>3769700826.5</v>
+      </c>
+      <c r="R3" s="4">
+        <f>'分析研究_经营性占款+高分红'!F8</f>
+        <v>893741863.21</v>
+      </c>
+      <c r="S3" s="4">
+        <f>'分析研究_经营性占款+高分红'!F9</f>
+        <v>321692953.88</v>
+      </c>
+      <c r="T3" s="4">
+        <f>'分析研究_经营性占款+高分红'!F10</f>
+        <v>254094791.55</v>
+      </c>
+      <c r="U3" s="4">
+        <f>'分析研究_经营性占款+高分红'!F13</f>
+        <v>0</v>
+      </c>
+      <c r="V3" s="4">
+        <f>'分析研究_经营性占款+高分红'!F16</f>
+        <v>29191343.78</v>
+      </c>
+      <c r="W3" s="4">
+        <f>'分析研究_经营性占款+高分红'!F17</f>
+        <v>157420210.81</v>
+      </c>
+      <c r="X3" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q3" s="21">
+      <c r="Y3" s="21">
         <f t="shared" si="1"/>
         <v>4.17232513427734e-7</v>
       </c>
-      <c r="R3" s="21" t="b">
-        <f t="shared" ref="R3:R19" si="2">L3=K3+J3</f>
+      <c r="Z3" s="21" t="b">
+        <f t="shared" ref="Z3:Z19" si="2">L3=K3+J3</f>
         <v>1</v>
       </c>
-      <c r="S3" s="21" t="b">
-        <f t="shared" ref="S3:S19" si="3">I3=G3+H3</f>
+      <c r="AA3" s="21" t="b">
+        <f t="shared" ref="AA3:AA19" si="3">I3=G3+H3</f>
         <v>1</v>
       </c>
-      <c r="T3" s="18" t="s">
+      <c r="AB3" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28">
+      <c r="A4" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="19" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20">
-      <c r="A4" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>28</v>
       </c>
       <c r="C4" s="20">
         <v>2022</v>
@@ -4002,32 +4112,64 @@
       <c r="O4" s="4">
         <v>7072690188.28</v>
       </c>
-      <c r="P4" s="21">
+      <c r="P4" s="4">
+        <f>'分析研究_经营性占款+高分红'!E6</f>
+        <v>1057611900</v>
+      </c>
+      <c r="Q4" s="4">
+        <f>'分析研究_经营性占款+高分红'!E7</f>
+        <v>2635521548.19</v>
+      </c>
+      <c r="R4" s="4">
+        <f>'分析研究_经营性占款+高分红'!E8</f>
+        <v>1153932879.53</v>
+      </c>
+      <c r="S4" s="4">
+        <f>'分析研究_经营性占款+高分红'!E9</f>
+        <v>289075428.5</v>
+      </c>
+      <c r="T4" s="4">
+        <f>'分析研究_经营性占款+高分红'!E10</f>
+        <v>204608713.27</v>
+      </c>
+      <c r="U4" s="4">
+        <f>'分析研究_经营性占款+高分红'!E13</f>
+        <v>0</v>
+      </c>
+      <c r="V4" s="4">
+        <f>'分析研究_经营性占款+高分红'!E16</f>
+        <v>41924940.24</v>
+      </c>
+      <c r="W4" s="4">
+        <f>'分析研究_经营性占款+高分红'!E17</f>
+        <v>150779916.58</v>
+      </c>
+      <c r="X4" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q4" s="21">
+      <c r="Y4" s="21">
         <f t="shared" si="1"/>
         <v>-2.30967998504639e-7</v>
       </c>
-      <c r="R4" s="21" t="b">
+      <c r="Z4" s="21" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="S4" s="21" t="b">
+      <c r="AA4" s="21" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="T4" s="18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20">
+      <c r="AB4" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28">
       <c r="A5" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" s="20">
         <v>2023</v>
@@ -4068,32 +4210,64 @@
       <c r="O5" s="4">
         <v>6381833057.37</v>
       </c>
-      <c r="P5" s="21">
+      <c r="P5" s="4">
+        <f>'分析研究_经营性占款+高分红'!D6</f>
+        <v>1235000000</v>
+      </c>
+      <c r="Q5" s="4">
+        <f>'分析研究_经营性占款+高分红'!D7</f>
+        <v>3165691101.96</v>
+      </c>
+      <c r="R5" s="4">
+        <f>'分析研究_经营性占款+高分红'!D8</f>
+        <v>862706076.18</v>
+      </c>
+      <c r="S5" s="4">
+        <f>'分析研究_经营性占款+高分红'!D9</f>
+        <v>332138705.28</v>
+      </c>
+      <c r="T5" s="4">
+        <f>'分析研究_经营性占款+高分红'!D10</f>
+        <v>346462733.51</v>
+      </c>
+      <c r="U5" s="4">
+        <f>'分析研究_经营性占款+高分红'!D13</f>
+        <v>199741167.36</v>
+      </c>
+      <c r="V5" s="4">
+        <f>'分析研究_经营性占款+高分红'!D16</f>
+        <v>47568255.43</v>
+      </c>
+      <c r="W5" s="4">
+        <f>'分析研究_经营性占款+高分红'!D17</f>
+        <v>177281125.36</v>
+      </c>
+      <c r="X5" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q5" s="21">
+      <c r="Y5" s="21">
         <f t="shared" si="1"/>
         <v>2.30967998504639e-7</v>
       </c>
-      <c r="R5" s="21" t="b">
+      <c r="Z5" s="21" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="S5" s="21" t="b">
+      <c r="AA5" s="21" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="T5" s="18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20">
+      <c r="AB5" s="18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28">
       <c r="A6" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="20">
         <v>2024</v>
@@ -4134,32 +4308,64 @@
       <c r="O6" s="4">
         <v>6461527323.28</v>
       </c>
-      <c r="P6" s="21">
+      <c r="P6" s="4">
+        <f>'分析研究_经营性占款+高分红'!C6</f>
+        <v>1282200000</v>
+      </c>
+      <c r="Q6" s="4">
+        <f>'分析研究_经营性占款+高分红'!C7</f>
+        <v>3161736072.4</v>
+      </c>
+      <c r="R6" s="4">
+        <f>'分析研究_经营性占款+高分红'!C8</f>
+        <v>1088405139.86</v>
+      </c>
+      <c r="S6" s="4">
+        <f>'分析研究_经营性占款+高分红'!C9</f>
+        <v>357563855.07</v>
+      </c>
+      <c r="T6" s="4">
+        <f>'分析研究_经营性占款+高分红'!C10</f>
+        <v>284299883.91</v>
+      </c>
+      <c r="U6" s="4">
+        <f>'分析研究_经营性占款+高分红'!C13</f>
+        <v>0</v>
+      </c>
+      <c r="V6" s="4">
+        <f>'分析研究_经营性占款+高分红'!C16</f>
+        <v>41987421.6</v>
+      </c>
+      <c r="W6" s="4">
+        <f>'分析研究_经营性占款+高分红'!C17</f>
+        <v>188428980.22</v>
+      </c>
+      <c r="X6" s="21">
         <f t="shared" si="0"/>
         <v>9.5367431640625e-7</v>
       </c>
-      <c r="Q6" s="21">
+      <c r="Y6" s="21">
         <f t="shared" si="1"/>
         <v>1.49011611938477e-7</v>
       </c>
-      <c r="R6" s="21" t="b">
+      <c r="Z6" s="21" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="S6" s="21" t="b">
+      <c r="AA6" s="21" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="T6" s="18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20">
+      <c r="AB6" s="18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28">
       <c r="A7" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" s="20">
         <v>2025</v>
@@ -4200,32 +4406,64 @@
       <c r="O7" s="22">
         <v>6318732884.85</v>
       </c>
-      <c r="P7" s="21">
+      <c r="P7" s="22">
+        <f>'分析研究_经营性占款+高分红'!B6</f>
+        <v>1293265904.28</v>
+      </c>
+      <c r="Q7" s="22">
+        <f>'分析研究_经营性占款+高分红'!B7</f>
+        <v>3508073774.7</v>
+      </c>
+      <c r="R7" s="22">
+        <f>'分析研究_经营性占款+高分红'!B8</f>
+        <v>966693982.29</v>
+      </c>
+      <c r="S7" s="22">
+        <f>'分析研究_经营性占款+高分红'!B9</f>
+        <v>393640167.78</v>
+      </c>
+      <c r="T7" s="22">
+        <f>'分析研究_经营性占款+高分红'!B10</f>
+        <v>336011117.28</v>
+      </c>
+      <c r="U7" s="22">
+        <f>'分析研究_经营性占款+高分红'!B13</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="22">
+        <f>'分析研究_经营性占款+高分红'!B16</f>
+        <v>79097068.05</v>
+      </c>
+      <c r="W7" s="22">
+        <f>'分析研究_经营性占款+高分红'!B17</f>
+        <v>160127971.91</v>
+      </c>
+      <c r="X7" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q7" s="21">
+      <c r="Y7" s="21">
         <f t="shared" si="1"/>
         <v>5.73694705963135e-7</v>
       </c>
-      <c r="R7" s="21" t="b">
+      <c r="Z7" s="21" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="S7" s="21" t="b">
+      <c r="AA7" s="21" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="T7" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20">
+      <c r="AB7" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28">
       <c r="A8" s="18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C8" s="20">
         <v>2022</v>
@@ -4266,32 +4504,40 @@
       <c r="O8" s="4">
         <v>3326979961.57</v>
       </c>
-      <c r="P8" s="21">
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
+      <c r="X8" s="21">
         <f t="shared" si="0"/>
         <v>-4.76837158203125e-7</v>
       </c>
-      <c r="Q8" s="21">
+      <c r="Y8" s="21">
         <f t="shared" si="1"/>
         <v>2.29105353355408e-7</v>
       </c>
-      <c r="R8" s="21" t="b">
+      <c r="Z8" s="21" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="S8" s="21" t="b">
+      <c r="AA8" s="21" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="T8" s="18" t="s">
+      <c r="AB8" s="18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28">
+      <c r="A9" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="19" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20">
-      <c r="A9" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>35</v>
       </c>
       <c r="C9" s="20">
         <v>2023</v>
@@ -4332,32 +4578,40 @@
       <c r="O9" s="4">
         <v>3486246962.01</v>
       </c>
-      <c r="P9" s="21">
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+      <c r="X9" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q9" s="21">
+      <c r="Y9" s="21">
         <f t="shared" si="1"/>
         <v>1.34110450744629e-7</v>
       </c>
-      <c r="R9" s="21" t="b">
+      <c r="Z9" s="21" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="S9" s="21" t="b">
+      <c r="AA9" s="21" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="T9" s="18" t="s">
+      <c r="AB9" s="18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28">
+      <c r="A10" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="19" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20">
-      <c r="A10" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>35</v>
       </c>
       <c r="C10" s="20">
         <v>2024</v>
@@ -4398,32 +4652,40 @@
       <c r="O10" s="4">
         <v>3493964844.93</v>
       </c>
-      <c r="P10" s="21">
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
+      <c r="X10" s="21">
         <f t="shared" si="0"/>
         <v>4.76837158203125e-7</v>
       </c>
-      <c r="Q10" s="21">
+      <c r="Y10" s="21">
         <f t="shared" si="1"/>
         <v>-2.67289578914642e-7</v>
       </c>
-      <c r="R10" s="21" t="b">
+      <c r="Z10" s="21" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="S10" s="21" t="b">
+      <c r="AA10" s="21" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="T10" s="18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20">
+      <c r="AB10" s="18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28">
       <c r="A11" s="18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" s="20">
         <v>2025</v>
@@ -4464,32 +4726,40 @@
       <c r="O11" s="4">
         <v>3604127903.12</v>
       </c>
-      <c r="P11" s="21">
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
+      <c r="X11" s="21">
         <f t="shared" si="0"/>
         <v>4.76837158203125e-7</v>
       </c>
-      <c r="Q11" s="21">
+      <c r="Y11" s="21">
         <f t="shared" si="1"/>
         <v>-2.98023223876953e-8</v>
       </c>
-      <c r="R11" s="21" t="b">
+      <c r="Z11" s="21" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="S11" s="21" t="b">
+      <c r="AA11" s="21" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="T11" s="18" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20">
+      <c r="AB11" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28">
       <c r="A12" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" s="20">
         <v>2022</v>
@@ -4530,32 +4800,40 @@
       <c r="O12" s="4">
         <v>2366739238.8</v>
       </c>
-      <c r="P12" s="21">
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4"/>
+      <c r="X12" s="21">
         <f t="shared" si="0"/>
         <v>-4.76837158203125e-7</v>
       </c>
-      <c r="Q12" s="21">
+      <c r="Y12" s="21">
         <f t="shared" si="1"/>
         <v>3.43323335982859e-7</v>
       </c>
-      <c r="R12" s="21" t="b">
+      <c r="Z12" s="21" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="S12" s="21" t="b">
+      <c r="AA12" s="21" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="T12" s="18" t="s">
+      <c r="AB12" s="18" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28">
+      <c r="A13" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="19" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20">
-      <c r="A13" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>40</v>
       </c>
       <c r="C13" s="20">
         <v>2023</v>
@@ -4596,32 +4874,40 @@
       <c r="O13" s="4">
         <v>2736439789.43</v>
       </c>
-      <c r="P13" s="21">
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4"/>
+      <c r="X13" s="21">
         <f t="shared" si="0"/>
         <v>4.76837158203125e-7</v>
       </c>
-      <c r="Q13" s="21">
+      <c r="Y13" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R13" s="21" t="b">
+      <c r="Z13" s="21" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="S13" s="21" t="b">
+      <c r="AA13" s="21" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="T13" s="18" t="s">
+      <c r="AB13" s="18" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28">
+      <c r="A14" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="19" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20">
-      <c r="A14" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>40</v>
       </c>
       <c r="C14" s="20">
         <v>2024</v>
@@ -4662,32 +4948,40 @@
       <c r="O14" s="4">
         <v>2910785979.72</v>
       </c>
-      <c r="P14" s="21">
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="4"/>
+      <c r="X14" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q14" s="21">
+      <c r="Y14" s="21">
         <f t="shared" si="1"/>
         <v>-4.32133674621582e-7</v>
       </c>
-      <c r="R14" s="21" t="b">
+      <c r="Z14" s="21" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="S14" s="21" t="b">
+      <c r="AA14" s="21" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="T14" s="18" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20">
+      <c r="AB14" s="18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28">
       <c r="A15" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="20">
         <v>2025</v>
@@ -4728,32 +5022,40 @@
       <c r="O15" s="4">
         <v>3166451608.83</v>
       </c>
-      <c r="P15" s="21">
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4"/>
+      <c r="T15" s="4"/>
+      <c r="U15" s="4"/>
+      <c r="V15" s="4"/>
+      <c r="W15" s="4"/>
+      <c r="X15" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q15" s="21">
+      <c r="Y15" s="21">
         <f t="shared" si="1"/>
         <v>-8.94069671630859e-8</v>
       </c>
-      <c r="R15" s="21" t="b">
+      <c r="Z15" s="21" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="S15" s="21" t="b">
+      <c r="AA15" s="21" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="T15" s="18" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20">
+      <c r="AB15" s="18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28">
       <c r="A16" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C16" s="20">
         <v>2022</v>
@@ -4794,32 +5096,40 @@
       <c r="O16" s="4">
         <v>7104407818.01</v>
       </c>
-      <c r="P16" s="21">
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4"/>
+      <c r="V16" s="4"/>
+      <c r="W16" s="4"/>
+      <c r="X16" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q16" s="21">
+      <c r="Y16" s="21">
         <f t="shared" si="1"/>
         <v>6.55651092529297e-7</v>
       </c>
-      <c r="R16" s="21" t="b">
+      <c r="Z16" s="21" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="S16" s="21" t="b">
+      <c r="AA16" s="21" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="T16" s="18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20">
+      <c r="AB16" s="18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28">
       <c r="A17" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17" s="20">
         <v>2023</v>
@@ -4860,32 +5170,40 @@
       <c r="O17" s="4">
         <v>7731746578.08</v>
       </c>
-      <c r="P17" s="21">
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
+      <c r="X17" s="21">
         <f t="shared" si="0"/>
         <v>-9.5367431640625e-7</v>
       </c>
-      <c r="Q17" s="21">
+      <c r="Y17" s="21">
         <f t="shared" si="1"/>
         <v>-1.49011611938477e-7</v>
       </c>
-      <c r="R17" s="21" t="b">
+      <c r="Z17" s="21" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="S17" s="21" t="b">
+      <c r="AA17" s="21" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="T17" s="18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20">
+      <c r="AB17" s="18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28">
       <c r="A18" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C18" s="20">
         <v>2024</v>
@@ -4926,32 +5244,40 @@
       <c r="O18" s="4">
         <v>8400143303.14</v>
       </c>
-      <c r="P18" s="21">
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="4"/>
+      <c r="U18" s="4"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="4"/>
+      <c r="X18" s="21">
         <f t="shared" si="0"/>
         <v>-9.5367431640625e-7</v>
       </c>
-      <c r="Q18" s="21">
+      <c r="Y18" s="21">
         <f t="shared" si="1"/>
         <v>6.55651092529297e-7</v>
       </c>
-      <c r="R18" s="21" t="b">
+      <c r="Z18" s="21" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="S18" s="21" t="b">
+      <c r="AA18" s="21" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="T18" s="18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20">
+      <c r="AB18" s="18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28">
       <c r="A19" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" s="20">
         <v>2025</v>
@@ -4992,28 +5318,36 @@
       <c r="O19" s="4">
         <v>8742472843.31</v>
       </c>
-      <c r="P19" s="21">
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="4"/>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4"/>
+      <c r="X19" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q19" s="21">
+      <c r="Y19" s="21">
         <f t="shared" si="1"/>
         <v>-2.98023223876953e-7</v>
       </c>
-      <c r="R19" s="21" t="b">
+      <c r="Z19" s="21" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="S19" s="21" t="b">
+      <c r="AA19" s="21" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="T19" s="18" t="s">
-        <v>33</v>
+      <c r="AB19" s="18" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:T19" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AB19" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5034,38 +5368,38 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="8" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="9" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="11" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="12">
         <f>IF(OR(SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B4,资产负债表!$C:$C,C$3)=0,SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B4,资产负债表!$C:$C,C$3-1)=0),"",SUMIFS(利润表!$O:$O,利润表!$B:$B,$B4,利润表!$C:$C,C$3)/((SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B4,资产负债表!$C:$C,C$3)+SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B4,资产负债表!$C:$C,C$3-1))/2))</f>
@@ -5090,10 +5424,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="11" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" s="12" t="str">
         <f>IF(OR(SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B5,资产负债表!$C:$C,C$3)=0,SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B5,资产负债表!$C:$C,C$3-1)=0),"",SUMIFS(利润表!$O:$O,利润表!$B:$B,$B5,利润表!$C:$C,C$3)/((SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B5,资产负债表!$C:$C,C$3)+SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B5,资产负债表!$C:$C,C$3-1))/2))</f>
@@ -5118,10 +5452,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="11" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6" s="12" t="str">
         <f>IF(OR(SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B6,资产负债表!$C:$C,C$3)=0,SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B6,资产负债表!$C:$C,C$3-1)=0),"",SUMIFS(利润表!$O:$O,利润表!$B:$B,$B6,利润表!$C:$C,C$3)/((SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B6,资产负债表!$C:$C,C$3)+SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B6,资产负债表!$C:$C,C$3-1))/2))</f>
@@ -5146,10 +5480,10 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="11" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7" s="12" t="str">
         <f>IF(OR(SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B7,资产负债表!$C:$C,C$3)=0,SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B7,资产负债表!$C:$C,C$3-1)=0),"",SUMIFS(利润表!$O:$O,利润表!$B:$B,$B7,利润表!$C:$C,C$3)/((SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B7,资产负债表!$C:$C,C$3)+SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B7,资产负债表!$C:$C,C$3-1))/2))</f>
@@ -5174,10 +5508,10 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="11" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" s="12">
         <f>IF(SUMIFS(利润表!$D:$D,利润表!$B:$B,$B9,利润表!$C:$C,C$3)=0,"",SUMIFS(利润表!$O:$O,利润表!$B:$B,$B9,利润表!$C:$C,C$3)/SUMIFS(利润表!$D:$D,利润表!$B:$B,$B9,利润表!$C:$C,C$3))</f>
@@ -5202,10 +5536,10 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="11" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" s="12" t="str">
         <f>IF(SUMIFS(利润表!$D:$D,利润表!$B:$B,$B10,利润表!$C:$C,C$3)=0,"",SUMIFS(利润表!$O:$O,利润表!$B:$B,$B10,利润表!$C:$C,C$3)/SUMIFS(利润表!$D:$D,利润表!$B:$B,$B10,利润表!$C:$C,C$3))</f>
@@ -5230,10 +5564,10 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="11" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" s="12" t="str">
         <f>IF(SUMIFS(利润表!$D:$D,利润表!$B:$B,$B11,利润表!$C:$C,C$3)=0,"",SUMIFS(利润表!$O:$O,利润表!$B:$B,$B11,利润表!$C:$C,C$3)/SUMIFS(利润表!$D:$D,利润表!$B:$B,$B11,利润表!$C:$C,C$3))</f>
@@ -5258,10 +5592,10 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="11" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C12" s="12" t="str">
         <f>IF(SUMIFS(利润表!$D:$D,利润表!$B:$B,$B12,利润表!$C:$C,C$3)=0,"",SUMIFS(利润表!$O:$O,利润表!$B:$B,$B12,利润表!$C:$C,C$3)/SUMIFS(利润表!$D:$D,利润表!$B:$B,$B12,利润表!$C:$C,C$3))</f>
@@ -5286,10 +5620,10 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="11" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C14" s="13">
         <f>IF(OR(SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B14,资产负债表!$C:$C,C$3)=0,SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B14,资产负债表!$C:$C,C$3-1)=0),"",SUMIFS(利润表!$D:$D,利润表!$B:$B,$B14,利润表!$C:$C,C$3)/((SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B14,资产负债表!$C:$C,C$3)+SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B14,资产负债表!$C:$C,C$3-1))/2))</f>
@@ -5314,10 +5648,10 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="11" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" s="13" t="str">
         <f>IF(OR(SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B15,资产负债表!$C:$C,C$3)=0,SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B15,资产负债表!$C:$C,C$3-1)=0),"",SUMIFS(利润表!$D:$D,利润表!$B:$B,$B15,利润表!$C:$C,C$3)/((SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B15,资产负债表!$C:$C,C$3)+SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B15,资产负债表!$C:$C,C$3-1))/2))</f>
@@ -5342,10 +5676,10 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="11" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" s="13" t="str">
         <f>IF(OR(SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B16,资产负债表!$C:$C,C$3)=0,SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B16,资产负债表!$C:$C,C$3-1)=0),"",SUMIFS(利润表!$D:$D,利润表!$B:$B,$B16,利润表!$C:$C,C$3)/((SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B16,资产负债表!$C:$C,C$3)+SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B16,资产负债表!$C:$C,C$3-1))/2))</f>
@@ -5370,10 +5704,10 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="11" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17" s="13" t="str">
         <f>IF(OR(SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B17,资产负债表!$C:$C,C$3)=0,SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B17,资产负债表!$C:$C,C$3-1)=0),"",SUMIFS(利润表!$D:$D,利润表!$B:$B,$B17,利润表!$C:$C,C$3)/((SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B17,资产负债表!$C:$C,C$3)+SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B17,资产负债表!$C:$C,C$3-1))/2))</f>
@@ -5398,10 +5732,10 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="11" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C19" s="13">
         <f>IF(OR(SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B19,资产负债表!$C:$C,C$3)=0,SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B19,资产负债表!$C:$C,C$3-1)=0,SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B19,资产负债表!$C:$C,C$3)=0,SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B19,资产负债表!$C:$C,C$3-1)=0),"",((SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B19,资产负债表!$C:$C,C$3)+SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B19,资产负债表!$C:$C,C$3-1))/2)/((SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B19,资产负债表!$C:$C,C$3)+SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B19,资产负债表!$C:$C,C$3-1))/2))</f>
@@ -5426,10 +5760,10 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="11" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C20" s="13" t="str">
         <f>IF(OR(SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B20,资产负债表!$C:$C,C$3)=0,SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B20,资产负债表!$C:$C,C$3-1)=0,SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B20,资产负债表!$C:$C,C$3)=0,SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B20,资产负债表!$C:$C,C$3-1)=0),"",((SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B20,资产负债表!$C:$C,C$3)+SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B20,资产负债表!$C:$C,C$3-1))/2)/((SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B20,资产负债表!$C:$C,C$3)+SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B20,资产负债表!$C:$C,C$3-1))/2))</f>
@@ -5454,10 +5788,10 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="11" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C21" s="13" t="str">
         <f>IF(OR(SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B21,资产负债表!$C:$C,C$3)=0,SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B21,资产负债表!$C:$C,C$3-1)=0,SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B21,资产负债表!$C:$C,C$3)=0,SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B21,资产负债表!$C:$C,C$3-1)=0),"",((SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B21,资产负债表!$C:$C,C$3)+SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B21,资产负债表!$C:$C,C$3-1))/2)/((SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B21,资产负债表!$C:$C,C$3)+SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B21,资产负债表!$C:$C,C$3-1))/2))</f>
@@ -5482,10 +5816,10 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="11" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C22" s="13" t="str">
         <f>IF(OR(SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B22,资产负债表!$C:$C,C$3)=0,SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B22,资产负债表!$C:$C,C$3-1)=0,SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B22,资产负债表!$C:$C,C$3)=0,SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B22,资产负债表!$C:$C,C$3-1)=0),"",((SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B22,资产负债表!$C:$C,C$3)+SUMIFS(资产负债表!$I:$I,资产负债表!$B:$B,$B22,资产负债表!$C:$C,C$3-1))/2)/((SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B22,资产负债表!$C:$C,C$3)+SUMIFS(资产负债表!$M:$M,资产负债表!$B:$B,$B22,资产负债表!$C:$C,C$3-1))/2))</f>
@@ -5510,10 +5844,10 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="14" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C24" s="15">
         <f>IF(OR(C9="",C14="",C19=""),"",C9*C14*C19)</f>
@@ -5538,10 +5872,10 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="14" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C25" s="15" t="str">
         <f t="shared" ref="C25:G25" si="1">IF(OR(C10="",C15="",C20=""),"",C10*C15*C20)</f>
@@ -5566,10 +5900,10 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="14" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C26" s="15" t="str">
         <f t="shared" ref="C26:G26" si="2">IF(OR(C11="",C16="",C21=""),"",C11*C16*C21)</f>
@@ -5594,10 +5928,10 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="14" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C27" s="15" t="str">
         <f t="shared" ref="C27:G27" si="3">IF(OR(C12="",C17="",C22=""),"",C12*C17*C22)</f>
@@ -5622,10 +5956,10 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="16" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C29" s="17" t="b">
         <f>C24=C4</f>
@@ -5650,10 +5984,10 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="16" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C30" s="17" t="b">
         <f t="shared" ref="C30:G30" si="5">C25=C5</f>
@@ -5678,10 +6012,10 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="16" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C31" s="17" t="b">
         <f t="shared" ref="C31:G31" si="6">C26=C6</f>
@@ -5706,10 +6040,10 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="16" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C32" s="17" t="b">
         <f t="shared" ref="C32:G32" si="7">C27=C7</f>
@@ -5771,7 +6105,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B2" s="3">
         <v>2095710650.28</v>
@@ -5792,7 +6126,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B3" s="4">
         <f>利润表!O6</f>
@@ -5817,7 +6151,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B4" s="6">
         <f>B2/B3</f>
@@ -5842,7 +6176,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B5" s="4">
         <f>资产负债表!L7</f>
@@ -5867,7 +6201,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="B6" s="3">
         <v>1293265904.28</v>
@@ -5887,7 +6221,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="B7" s="3">
         <v>3508073774.7</v>
@@ -5907,7 +6241,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="B8" s="3">
         <v>966693982.29</v>
@@ -5927,7 +6261,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="B9" s="3">
         <v>393640167.78</v>
@@ -5947,7 +6281,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="B10" s="3">
         <v>336011117.28</v>
@@ -5967,7 +6301,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="7" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B11" s="3">
         <f>SUM(B6:B10)</f>
@@ -5992,7 +6326,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B12" s="6">
         <f>B11/B5</f>
@@ -6017,7 +6351,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -6037,7 +6371,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -6057,7 +6391,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -6077,7 +6411,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="B16" s="3">
         <v>79097068.05</v>
@@ -6097,7 +6431,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="B17" s="3">
         <v>160127971.91</v>
@@ -6117,7 +6451,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B18">
         <f>SUM(B13:B17)</f>
@@ -6142,7 +6476,7 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B19" s="4">
         <f>资产负债表!I7</f>
@@ -6167,7 +6501,7 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B20" s="6">
         <f>B18/B19</f>
